--- a/MainTop/Остатки_бирки/остатки_бирки3.xlsx
+++ b/MainTop/Остатки_бирки/остатки_бирки3.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\Остатки_бирки\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73780DE-5011-4687-A545-C259FBD01F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1476D7-D4BD-448B-B4E6-0B55E372CC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -377,7 +377,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
